--- a/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,122 +626,102 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9187
-</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
@@ -762,146 +742,122 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2939
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1535
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -918,32 +874,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -953,104 +904,87 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1072,146 +1006,122 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
-</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1228,68 +1138,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
-</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1299,74 +1198,62 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,38 +1270,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11185
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1429,92 +1310,77 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
-</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
-</t>
+          <t>601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
-</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
-</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr"/>
@@ -1532,141 +1398,118 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97 9
-</t>
+          <t>22 95</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,26 +1531,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1717,44 +1556,37 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1764,63 +1596,34 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406491
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11812 1
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02 4
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1835,109 +1638,92 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
-</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
@@ -1949,8 +1735,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1960,8 +1745,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1978,146 +1762,122 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2134,146 +1894,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
-</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,146 +2026,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
-</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0911
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2446,14 +2158,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475
-</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2463,20 +2173,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2486,20 +2193,17 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2509,20 +2213,17 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11404
-</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2532,8 +2233,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2543,44 +2243,37 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3945
-</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12088
-</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2597,140 +2290,117 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2950
-</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 14
-</t>
+          <t>0 14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2695
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>021</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>789</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2752,26 +2422,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4283
-</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2781,20 +2447,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2804,26 +2467,22 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -2834,14 +2493,12 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2851,8 +2508,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2862,14 +2518,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2879,8 +2533,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2897,146 +2550,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
-</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3053,38 +2682,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3094,20 +2717,17 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -3117,80 +2737,67 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3207,146 +2814,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
-</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>908</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3363,134 +2946,112 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3500,8 +3061,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3523,39 +3083,33 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3565,14 +3119,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3582,50 +3134,42 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
-</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3640,14 +3184,12 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9295
-</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3664,146 +3206,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154
-</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10434
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3820,26 +3338,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3864,51 +3378,43 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3923,14 +3429,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
@@ -3940,14 +3444,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3964,146 +3466,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4120,141 +3598,118 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7170
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4271,98 +3726,82 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -4372,44 +3811,37 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
-</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4426,146 +3858,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
-</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4582,21 +3990,18 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
-</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11298
-</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4606,39 +4011,33 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>717</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>792</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4653,62 +4052,52 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610
-</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410
-</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4725,136 +4114,114 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181 1</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4871,33 +4238,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4907,20 +4269,17 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4930,80 +4289,67 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5020,146 +4366,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14828
-</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5176,14 +4498,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5193,122 +4513,102 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11095
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z34" s="2" t="n"/>
@@ -5326,32 +4626,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94928
-</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5366,104 +4661,87 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9100
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2945
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6008
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5480,146 +4758,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94989
-</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2942
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>790</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5636,14 +4890,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21928
-</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -5658,110 +4910,89 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">757
-</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7112
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
-        </is>
-      </c>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3134
-</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
-</t>
+          <t>804</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4098
-</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5783,50 +5014,42 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">438
-</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -5837,86 +5060,72 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>627</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5933,69 +5142,58 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">395953
-</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>016</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -6005,32 +5203,27 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -6041,14 +5234,12 @@
       <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -6080,32 +5271,27 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -6120,98 +5306,82 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6228,146 +5398,122 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
-</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6384,146 +5530,122 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6540,146 +5662,122 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571
-</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1354
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6696,141 +5794,118 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
-</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1836
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">593
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6847,146 +5922,122 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29830
-</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
-</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911
-</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53409
-</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3510
-</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11115
-</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4668
-</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7003,146 +6054,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4970
-</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>080</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
